--- a/40_数据库/学习笔记_RDBMS_PostgreSql.xlsx
+++ b/40_数据库/学习笔记_RDBMS_PostgreSql.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="概述" sheetId="1" r:id="rId1"/>
@@ -53915,9 +53915,9 @@
       </c>
       <c r="I3" s="100" t="str">
         <f>IF(G3="是",IF(H3="新增",CONCATENATE("alter table ",C3," add primary key (",D3,");"),CONCATENATE("alter table ",C3," DROP CONSTRAINT ",E3,";")),
-IF(F3="是",IF(H3="新增",CONCATENATE("CREATE UNIQUE INDEX ",E3," ON public. ",C3," (",D3,");"),CONCATENATE("DROP INDEX ",E3,";")),
-IF(H3="新增",CONCATENATE("CREATE INDEX ",E3," ON public. ",C3," (",D3,");"),CONCATENATE("DROP  index ",E3,";"))))</f>
-        <v>CREATE INDEX IDX_DLR3 ON public. T_OMS_APP_BU_VOICE_BIND_USER (DLR_ID,CREATED_DATE,ACCOUNT_CODE);</v>
+IF(F3="是",IF(H3="新增",CONCATENATE("CREATE UNIQUE INDEX ",E3," ON ",C3," (",D3,");"),CONCATENATE("DROP INDEX ",E3,";")),
+IF(H3="新增",CONCATENATE("CREATE INDEX ",E3," ON ",C3," (",D3,");"),CONCATENATE("DROP  index ",E3,";"))))</f>
+        <v>CREATE INDEX IDX_DLR3 ON T_OMS_APP_BU_VOICE_BIND_USER (DLR_ID,CREATED_DATE,ACCOUNT_CODE);</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75">
@@ -53944,9 +53944,9 @@
       </c>
       <c r="I4" s="100" t="str">
         <f t="shared" ref="I4:I7" si="0">IF(G4="是",IF(H4="新增",CONCATENATE("alter table ",C4," add primary key (",D4,");"),CONCATENATE("alter table ",C4," DROP CONSTRAINT ",E4,";")),
-IF(F4="是",IF(H4="新增",CONCATENATE("CREATE UNIQUE INDEX ",E4," ON public. ",C4," (",D4,");"),CONCATENATE("DROP INDEX ",E4,";")),
-IF(H4="新增",CONCATENATE("CREATE INDEX ",E4," ON public. ",C4," (",D4,");"),CONCATENATE("DROP  index ",E4,";"))))</f>
-        <v>CREATE UNIQUE INDEX UK_ACCOUNT_INFO_CODE2 ON public. T_OMS_APP_BU_VOICE_BIND_USER (ACCOUNT_INFO_CODE,MODULE_CODE);</v>
+IF(F4="是",IF(H4="新增",CONCATENATE("CREATE UNIQUE INDEX ",E4," ON ",C4," (",D4,");"),CONCATENATE("DROP INDEX ",E4,";")),
+IF(H4="新增",CONCATENATE("CREATE INDEX ",E4," ON ",C4," (",D4,");"),CONCATENATE("DROP  index ",E4,";"))))</f>
+        <v>CREATE UNIQUE INDEX UK_ACCOUNT_INFO_CODE2 ON T_OMS_APP_BU_VOICE_BIND_USER (ACCOUNT_INFO_CODE,MODULE_CODE);</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75">
@@ -53973,7 +53973,7 @@
       </c>
       <c r="I5" s="100" t="str">
         <f t="shared" si="0"/>
-        <v>CREATE INDEX IDX_CREATED_DATE ON public. T_OMS_APP_BU_VOICE_BIND_USER (CREATED_DATE);</v>
+        <v>CREATE INDEX IDX_CREATED_DATE ON T_OMS_APP_BU_VOICE_BIND_USER (CREATED_DATE);</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75">
@@ -54000,7 +54000,7 @@
       </c>
       <c r="I6" s="100" t="str">
         <f t="shared" si="0"/>
-        <v>CREATE INDEX IDX_LAST_UPDATED_DATE ON public. T_OMS_APP_BU_VOICE_BIND_USER (LAST_UPDATED_DATE);</v>
+        <v>CREATE INDEX IDX_LAST_UPDATED_DATE ON T_OMS_APP_BU_VOICE_BIND_USER (LAST_UPDATED_DATE);</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75">

--- a/40_数据库/学习笔记_RDBMS_PostgreSql.xlsx
+++ b/40_数据库/学习笔记_RDBMS_PostgreSql.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B8BD9D-C9AD-40DC-A19E-BC50638F63A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概述" sheetId="1" r:id="rId1"/>
@@ -21,7 +22,7 @@
     <sheet name="类型" sheetId="9" r:id="rId12"/>
     <sheet name="参考" sheetId="7" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28418,9 +28419,6 @@
     </r>
   </si>
   <si>
-    <t>方法1：使用子查询</t>
-  </si>
-  <si>
     <r>
       <t>你可以在</t>
     </r>
@@ -28516,13 +28514,6 @@
     </r>
   </si>
   <si>
-    <t>UPDATE employees
-SET department_name = sub.department_name
-FROM departments sub
-WHERE employees.department_id = sub.department_id;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>在这个例子中，我们从</t>
     </r>
@@ -28579,30 +28570,6 @@
         <family val="2"/>
       </rPr>
       <t>字段。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>方法2：使用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial Unicode MS"/>
-        <charset val="134"/>
-      </rPr>
-      <t>UPDATE ... FROM</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="13.5"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>结构（PostgreSQL 11及以上版本）</t>
     </r>
   </si>
   <si>
@@ -28655,9 +28622,6 @@
   </si>
   <si>
     <t>这种方法更加直观和符合SQL标准。</t>
-  </si>
-  <si>
-    <t>方法3：使用临时表或CTE（公用表表达式）</t>
   </si>
   <si>
     <t>如果你需要更复杂的逻辑，可以先在临时表或CTE中执行复杂的查询，然后再用结果更新表。</t>
@@ -28673,9 +28637,6 @@
 FROM updated_dept ud
 WHERE employees.employee_id = ud.employee_id;</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>方法4：使用PL/pgSQL函数（如果需要更复杂的逻辑）</t>
   </si>
   <si>
     <t>如果更新逻辑非常复杂，或者需要基于多个条件动态地选择更新哪些行，你可以使用PL/pgSQL编写一个函数：</t>
@@ -28851,15 +28812,244 @@
 UPDATE employees SET bonus = CASE WHEN NULLIF(bonus, salary) IS NULL THEN 0 ELSE bonus END;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>方法</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：使用子查询</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>方法</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
+      </rPr>
+      <t>UPDATE ... FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>结构（</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>PostgreSQL 11</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>及以上版本）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UPDATE employees
+SET salary = (SELECT AVG(salary) FROM employees) * 1.1
+WHERE department = 'Sales';</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>方法</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：使用临时表或</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>CTE</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（公用表表达式）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>方法</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：使用</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>PL/pgSQL</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13.5"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>函数（如果需要更复杂的逻辑）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yy/m/d;@"/>
   </numFmts>
-  <fonts count="88">
+  <fonts count="90">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -29478,6 +29668,22 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color rgb="FF333333"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -29648,7 +29854,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -29977,12 +30183,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="3"/>
-    <cellStyle name="常规 2 10" xfId="4"/>
-    <cellStyle name="常规_数据库变更记录_090415客户" xfId="2"/>
+    <cellStyle name="常规 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="常规 2 10" xfId="4" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="常规_数据库变更记录_090415客户" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="2">
@@ -30010,7 +30219,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -30288,7 +30497,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B45"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -30514,18 +30723,18 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:11" ht="18">
       <c r="A1" s="113" t="s">
-        <v>1565</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="B2" s="122" t="s">
-        <v>1564</v>
+        <v>1559</v>
       </c>
       <c r="C2" s="122"/>
       <c r="D2" s="122"/>
@@ -30539,12 +30748,12 @@
     </row>
     <row r="11" spans="1:11" ht="18">
       <c r="A11" s="113" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="B12" s="121" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="C12" s="121"/>
       <c r="D12" s="121"/>
@@ -30567,8 +30776,8 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H62"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:H60"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:8" ht="23.25">
@@ -30709,91 +30918,91 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="17.25">
-      <c r="B19" s="111" t="s">
-        <v>1543</v>
+    <row r="19" spans="2:8" ht="20.25">
+      <c r="B19" s="126" t="s">
+        <v>1569</v>
       </c>
     </row>
     <row r="20" spans="2:8">
       <c r="B20" s="9" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" s="124" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C22" s="125"/>
+      <c r="D22" s="125"/>
+      <c r="E22" s="125"/>
+      <c r="F22" s="125"/>
+      <c r="G22" s="125"/>
+      <c r="H22" s="125"/>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" s="125"/>
+      <c r="C23" s="125"/>
+      <c r="D23" s="125"/>
+      <c r="E23" s="125"/>
+      <c r="F23" s="125"/>
+      <c r="G23" s="125"/>
+      <c r="H23" s="125"/>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24" s="125"/>
+      <c r="C24" s="125"/>
+      <c r="D24" s="125"/>
+      <c r="E24" s="125"/>
+      <c r="F24" s="125"/>
+      <c r="G24" s="125"/>
+      <c r="H24" s="125"/>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25" s="125"/>
+      <c r="C25" s="125"/>
+      <c r="D25" s="125"/>
+      <c r="E25" s="125"/>
+      <c r="F25" s="125"/>
+      <c r="G25" s="125"/>
+      <c r="H25" s="125"/>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26" s="9" t="s">
         <v>1544</v>
       </c>
     </row>
-    <row r="22" spans="2:8">
-      <c r="B22" s="120" t="s">
-        <v>1545</v>
-      </c>
-      <c r="C22" s="121"/>
-      <c r="D22" s="121"/>
-      <c r="E22" s="121"/>
-      <c r="F22" s="121"/>
-      <c r="G22" s="121"/>
-      <c r="H22" s="121"/>
-    </row>
-    <row r="23" spans="2:8">
-      <c r="B23" s="121"/>
-      <c r="C23" s="121"/>
-      <c r="D23" s="121"/>
-      <c r="E23" s="121"/>
-      <c r="F23" s="121"/>
-      <c r="G23" s="121"/>
-      <c r="H23" s="121"/>
-    </row>
-    <row r="24" spans="2:8">
-      <c r="B24" s="121"/>
-      <c r="C24" s="121"/>
-      <c r="D24" s="121"/>
-      <c r="E24" s="121"/>
-      <c r="F24" s="121"/>
-      <c r="G24" s="121"/>
-      <c r="H24" s="121"/>
-    </row>
-    <row r="25" spans="2:8">
-      <c r="B25" s="121"/>
-      <c r="C25" s="121"/>
-      <c r="D25" s="121"/>
-      <c r="E25" s="121"/>
-      <c r="F25" s="121"/>
-      <c r="G25" s="121"/>
-      <c r="H25" s="121"/>
-    </row>
-    <row r="26" spans="2:8">
-      <c r="B26" s="121"/>
-      <c r="C26" s="121"/>
-      <c r="D26" s="121"/>
-      <c r="E26" s="121"/>
-      <c r="F26" s="121"/>
-      <c r="G26" s="121"/>
-      <c r="H26" s="121"/>
-    </row>
-    <row r="27" spans="2:8">
-      <c r="B27" s="121"/>
-      <c r="C27" s="121"/>
-      <c r="D27" s="121"/>
-      <c r="E27" s="121"/>
-      <c r="F27" s="121"/>
-      <c r="G27" s="121"/>
-      <c r="H27" s="121"/>
+    <row r="27" spans="2:8" ht="20.25">
+      <c r="B27" s="126" t="s">
+        <v>1570</v>
+      </c>
     </row>
     <row r="28" spans="2:8">
       <c r="B28" s="9" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" s="124" t="s">
         <v>1546</v>
       </c>
-    </row>
-    <row r="29" spans="2:8" ht="17.25">
-      <c r="B29" s="111" t="s">
-        <v>1547</v>
-      </c>
+      <c r="C29" s="125"/>
+      <c r="D29" s="125"/>
+      <c r="E29" s="125"/>
+      <c r="F29" s="125"/>
+      <c r="G29" s="125"/>
+      <c r="H29" s="125"/>
     </row>
     <row r="30" spans="2:8">
-      <c r="B30" s="9" t="s">
-        <v>1548</v>
-      </c>
+      <c r="B30" s="125"/>
+      <c r="C30" s="125"/>
+      <c r="D30" s="125"/>
+      <c r="E30" s="125"/>
+      <c r="F30" s="125"/>
+      <c r="G30" s="125"/>
+      <c r="H30" s="125"/>
     </row>
     <row r="31" spans="2:8">
-      <c r="B31" s="124" t="s">
-        <v>1549</v>
-      </c>
+      <c r="B31" s="125"/>
       <c r="C31" s="125"/>
       <c r="D31" s="125"/>
       <c r="E31" s="125"/>
@@ -30829,42 +31038,42 @@
       <c r="H34" s="125"/>
     </row>
     <row r="35" spans="2:8">
-      <c r="B35" s="125"/>
-      <c r="C35" s="125"/>
-      <c r="D35" s="125"/>
-      <c r="E35" s="125"/>
-      <c r="F35" s="125"/>
-      <c r="G35" s="125"/>
-      <c r="H35" s="125"/>
-    </row>
-    <row r="36" spans="2:8">
-      <c r="B36" s="125"/>
-      <c r="C36" s="125"/>
-      <c r="D36" s="125"/>
-      <c r="E36" s="125"/>
-      <c r="F36" s="125"/>
-      <c r="G36" s="125"/>
-      <c r="H36" s="125"/>
+      <c r="B35" s="9" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" ht="20.25">
+      <c r="B36" s="126" t="s">
+        <v>1572</v>
+      </c>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" s="9" t="s">
-        <v>1550</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8" ht="17.25">
-      <c r="B38" s="111" t="s">
-        <v>1551</v>
-      </c>
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8">
+      <c r="B38" s="124" t="s">
+        <v>1549</v>
+      </c>
+      <c r="C38" s="125"/>
+      <c r="D38" s="125"/>
+      <c r="E38" s="125"/>
+      <c r="F38" s="125"/>
+      <c r="G38" s="125"/>
+      <c r="H38" s="125"/>
     </row>
     <row r="39" spans="2:8">
-      <c r="B39" s="9" t="s">
-        <v>1552</v>
-      </c>
+      <c r="B39" s="124"/>
+      <c r="C39" s="125"/>
+      <c r="D39" s="125"/>
+      <c r="E39" s="125"/>
+      <c r="F39" s="125"/>
+      <c r="G39" s="125"/>
+      <c r="H39" s="125"/>
     </row>
     <row r="40" spans="2:8">
-      <c r="B40" s="124" t="s">
-        <v>1553</v>
-      </c>
+      <c r="B40" s="124"/>
       <c r="C40" s="125"/>
       <c r="D40" s="125"/>
       <c r="E40" s="125"/>
@@ -30891,7 +31100,7 @@
       <c r="H42" s="125"/>
     </row>
     <row r="43" spans="2:8">
-      <c r="B43" s="124"/>
+      <c r="B43" s="125"/>
       <c r="C43" s="125"/>
       <c r="D43" s="125"/>
       <c r="E43" s="125"/>
@@ -30900,7 +31109,7 @@
       <c r="H43" s="125"/>
     </row>
     <row r="44" spans="2:8">
-      <c r="B44" s="124"/>
+      <c r="B44" s="125"/>
       <c r="C44" s="125"/>
       <c r="D44" s="125"/>
       <c r="E44" s="125"/>
@@ -30935,38 +31144,38 @@
       <c r="G47" s="125"/>
       <c r="H47" s="125"/>
     </row>
-    <row r="48" spans="2:8">
-      <c r="B48" s="125"/>
-      <c r="C48" s="125"/>
-      <c r="D48" s="125"/>
-      <c r="E48" s="125"/>
-      <c r="F48" s="125"/>
-      <c r="G48" s="125"/>
-      <c r="H48" s="125"/>
+    <row r="48" spans="2:8" ht="20.25">
+      <c r="B48" s="126" t="s">
+        <v>1573</v>
+      </c>
     </row>
     <row r="49" spans="2:8">
-      <c r="B49" s="125"/>
-      <c r="C49" s="125"/>
-      <c r="D49" s="125"/>
-      <c r="E49" s="125"/>
-      <c r="F49" s="125"/>
-      <c r="G49" s="125"/>
-      <c r="H49" s="125"/>
-    </row>
-    <row r="50" spans="2:8" ht="17.25">
-      <c r="B50" s="111" t="s">
-        <v>1554</v>
-      </c>
+      <c r="B49" s="9" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8">
+      <c r="B50" s="124" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C50" s="125"/>
+      <c r="D50" s="125"/>
+      <c r="E50" s="125"/>
+      <c r="F50" s="125"/>
+      <c r="G50" s="125"/>
+      <c r="H50" s="125"/>
     </row>
     <row r="51" spans="2:8">
-      <c r="B51" s="9" t="s">
-        <v>1555</v>
-      </c>
+      <c r="B51" s="125"/>
+      <c r="C51" s="125"/>
+      <c r="D51" s="125"/>
+      <c r="E51" s="125"/>
+      <c r="F51" s="125"/>
+      <c r="G51" s="125"/>
+      <c r="H51" s="125"/>
     </row>
     <row r="52" spans="2:8">
-      <c r="B52" s="124" t="s">
-        <v>1556</v>
-      </c>
+      <c r="B52" s="125"/>
       <c r="C52" s="125"/>
       <c r="D52" s="125"/>
       <c r="E52" s="125"/>
@@ -31020,45 +31229,27 @@
       <c r="H57" s="125"/>
     </row>
     <row r="58" spans="2:8">
-      <c r="B58" s="125"/>
-      <c r="C58" s="125"/>
-      <c r="D58" s="125"/>
-      <c r="E58" s="125"/>
-      <c r="F58" s="125"/>
-      <c r="G58" s="125"/>
-      <c r="H58" s="125"/>
-    </row>
-    <row r="59" spans="2:8">
-      <c r="B59" s="125"/>
-      <c r="C59" s="125"/>
-      <c r="D59" s="125"/>
-      <c r="E59" s="125"/>
-      <c r="F59" s="125"/>
-      <c r="G59" s="125"/>
-      <c r="H59" s="125"/>
+      <c r="B58" s="9" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" ht="17.25">
+      <c r="B59" s="111" t="s">
+        <v>1553</v>
+      </c>
     </row>
     <row r="60" spans="2:8">
       <c r="B60" s="9" t="s">
-        <v>1557</v>
-      </c>
-    </row>
-    <row r="61" spans="2:8" ht="17.25">
-      <c r="B61" s="111" t="s">
-        <v>1558</v>
-      </c>
-    </row>
-    <row r="62" spans="2:8">
-      <c r="B62" s="9" t="s">
-        <v>1559</v>
+        <v>1554</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:H15"/>
-    <mergeCell ref="B22:H27"/>
-    <mergeCell ref="B31:H36"/>
-    <mergeCell ref="B40:H49"/>
-    <mergeCell ref="B52:H59"/>
+    <mergeCell ref="B22:H25"/>
+    <mergeCell ref="B29:H34"/>
+    <mergeCell ref="B38:H47"/>
+    <mergeCell ref="B50:H57"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -31066,7 +31257,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
@@ -31076,7 +31267,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -31113,16 +31304,16 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B5" r:id="rId1"/>
-    <hyperlink ref="B2" r:id="rId2"/>
-    <hyperlink ref="B8" r:id="rId3"/>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{00000000-0004-0000-0C00-000000000000}"/>
+    <hyperlink ref="B2" r:id="rId2" xr:uid="{00000000-0004-0000-0C00-000001000000}"/>
+    <hyperlink ref="B8" r:id="rId3" xr:uid="{00000000-0004-0000-0C00-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J579"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -33005,7 +33196,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -33449,7 +33640,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G2055"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -52558,15 +52749,15 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B639" r:id="rId1" tooltip="操作系统知识库" display="http://lib.csdn.net/base/operatingsystem"/>
-    <hyperlink ref="B1079" r:id="rId2" tooltip="算法与数据结构知识库" display="http://lib.csdn.net/base/datastructure"/>
+    <hyperlink ref="B639" r:id="rId1" tooltip="操作系统知识库" display="http://lib.csdn.net/base/operatingsystem" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
+    <hyperlink ref="B1079" r:id="rId2" tooltip="算法与数据结构知识库" display="http://lib.csdn.net/base/datastructure" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:B198"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -53547,28 +53738,28 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:2" ht="20.25">
       <c r="A1" s="105" t="s">
-        <v>1560</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="B2" t="s">
-        <v>1561</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="20.25">
       <c r="A4" s="105" t="s">
-        <v>1562</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="18.75">
       <c r="B5" s="112" t="s">
-        <v>1563</v>
+        <v>1558</v>
       </c>
     </row>
   </sheetData>
@@ -53578,7 +53769,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G47"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -53722,22 +53913,22 @@
     </row>
     <row r="33" spans="1:7" ht="23.25">
       <c r="A33" s="110" t="s">
-        <v>1569</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="B34" s="7" t="s">
-        <v>1570</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="B35" t="s">
-        <v>1571</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="B36" s="120" t="s">
-        <v>1568</v>
+        <v>1563</v>
       </c>
       <c r="C36" s="121"/>
       <c r="D36" s="121"/>
@@ -53843,7 +54034,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
@@ -54033,10 +54224,10 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H6" xr:uid="{00000000-0002-0000-0700-000000000000}">
       <formula1>"新增,删除"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:G6 G3:G4 G7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:G6 G3:G4 G7" xr:uid="{00000000-0002-0000-0700-000001000000}">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -54045,18 +54236,18 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:9" ht="20.25">
       <c r="A1" s="105" t="s">
-        <v>1572</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.25" customHeight="1">
       <c r="B2" s="120" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="C2" s="120"/>
       <c r="D2" s="120"/>
